--- a/docs/downloads/04/tbl_homeland_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/04/tbl_homeland_marovoay_madiromiongana.xlsx
@@ -420,12 +420,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -465,12 +459,6 @@
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>8.5</v>
       </c>
     </row>
     <row r="6">
